--- a/output/pdf_financials_xlsx/DNG.xlsx
+++ b/output/pdf_financials_xlsx/DNG.xlsx
@@ -2117,40 +2117,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5346030000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.43892</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>14.011267</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.145339</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.191199</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.847281</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>13.92898</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>27.099182</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>25.595402</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>22.480659</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>19.819162</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>33.48778</v>
       </c>
     </row>
     <row r="35">
@@ -2213,40 +2213,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.07611800000000001</v>
+        <v>0.610721</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.72</v>
+        <v>4.15892</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>14.011267</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.145339</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.191199</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.847281</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>13.92898</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>27.099182</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>25.595402</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>22.480659</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>5.998457</v>
+        <v>25.817619</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>33.48778</v>
       </c>
     </row>
     <row r="37">
@@ -2789,40 +2789,40 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.598156</v>
+        <v>0.063553</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.625692</v>
+        <v>0.186772</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.538697</v>
+        <v>0.393358</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.390674</v>
+        <v>1.199475</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.431135</v>
+        <v>0.583854</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>14.051786</v>
+        <v>0.122806</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>27.239159</v>
+        <v>0.139977</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>26.190389</v>
+        <v>0.594987</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>22.757562</v>
+        <v>0.276903</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.179854</v>
+        <v>0.360692</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>36.161171</v>
+        <v>2.673391</v>
       </c>
     </row>
     <row r="49">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">

--- a/output/pdf_financials_xlsx/DNG.xlsx
+++ b/output/pdf_financials_xlsx/DNG.xlsx
@@ -5982,22 +5982,22 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.08720899999999999</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.417507</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.13815</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.15191</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.118103</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -14969,7 +14969,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
